--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M12B1_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M12B1_IN_Piura.xlsx
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.04</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>3.34</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>29.05</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="C13" s="28">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>51.87</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>15.7</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1910,11 +1910,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>268.3932</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1935,11 +1935,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>9.0838</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>3.38</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1960,11 +1960,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>259.3094</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>96.62</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2158,11 +2158,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>268.469</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2281,6 +2281,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2365,6 +2366,7 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="17" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2409,6 +2411,7 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="168" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -2661,11 +2664,11 @@
       </c>
       <c r="B13" s="32">
         <f>SUM(B10:B12)</f>
-        <v/>
+        <v>527.72</v>
       </c>
       <c r="C13" s="23">
         <f>SUM(C10:C12)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
@@ -2675,19 +2678,19 @@
       <c r="E13" s="17" t="inlineStr"/>
       <c r="F13" s="17">
         <f>ROUND(AVERAGE(F10:F12),2)</f>
-        <v/>
+        <v>27.57</v>
       </c>
       <c r="G13" s="22">
         <f>ROUND(AVERAGE(G10:G12),4)</f>
-        <v/>
+        <v>0.4547</v>
       </c>
       <c r="H13" s="23">
         <f>ROUND(AVERAGE(H10:H12),2)</f>
-        <v/>
+        <v>31.45</v>
       </c>
       <c r="I13" s="23">
         <f>ROUND(AVERAGE(I10:I12),2)</f>
-        <v/>
+        <v>68.55</v>
       </c>
     </row>
     <row r="14"/>
